--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_0_bus.xlsx
@@ -68,19 +68,19 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
-  </si>
-  <si>
     <t>Bus_1</t>
-  </si>
-  <si>
-    <t>Bus_2</t>
   </si>
   <si>
     <t>Bus_3</t>
   </si>
   <si>
     <t>Bus_4</t>
+  </si>
+  <si>
+    <t>Bus_0</t>
+  </si>
+  <si>
+    <t>Bus_2</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -526,22 +526,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>5.248639108480242</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1000.000056712887</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1.324394473835047</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>13.24394453564036</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940677566904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.248639108480242</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1000.000056712887</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1.324394473835047</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13.24394453564036</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.28940677566904</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -707,7 +707,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108526413</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108526413</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382473001</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108480242</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382473001</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195792622</v>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195792622</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138756735</v>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6080,7 +6080,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138756735</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8238,7 +8238,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498489</v>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8520,7 +8520,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8768,7 +8768,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8902,7 +8902,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9088,7 +9088,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9284,7 +9284,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -9346,7 +9346,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9408,7 +9408,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9627,7 +9627,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498488</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9775,7 +9775,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195753388</v>
@@ -9798,7 +9798,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195753388</v>
@@ -9946,7 +9946,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9969,7 +9969,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10015,7 +10015,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10140,7 +10140,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10163,7 +10163,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10242,7 +10242,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10265,7 +10265,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10403,7 +10403,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -10462,7 +10462,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10521,7 +10521,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10639,7 +10639,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>

--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_0_bus.xlsx
@@ -601,7 +601,7 @@
         <v>1000.000056712887</v>
       </c>
       <c r="D5">
-        <v>1.324394473835047</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E5">
         <v>13.24394453564036</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>84.28940677566904</v>
+        <v>84.28940677566905</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -713,19 +713,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.545454803106411</v>
+        <v>4.545454803106412</v>
       </c>
       <c r="D2">
-        <v>4.545454803106411</v>
+        <v>4.545454803106412</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>288.675150957904</v>
+        <v>288.6751509579041</v>
       </c>
       <c r="G2">
-        <v>288.675150957904</v>
+        <v>288.6751509579041</v>
       </c>
       <c r="H2">
         <v>1.324394477419423</v>
@@ -737,10 +737,10 @@
         <v>1.324394473632982</v>
       </c>
       <c r="K2">
-        <v>13.24394453600777</v>
+        <v>13.24394453600776</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -755,7 +755,7 @@
         <v>0.9526279647833883</v>
       </c>
       <c r="Q2">
-        <v>-8.694030303046307E-11</v>
+        <v>-8.694094919219585E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279646671958</v>
+        <v>0.9526279646671957</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648965608</v>
+        <v>0.9526279648965609</v>
       </c>
       <c r="Q3">
-        <v>1.457268468660959E-10</v>
+        <v>1.457467059280777E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999998456</v>
+        <v>179.9999999998455</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -873,13 +873,13 @@
         <v>0.9526279649233321</v>
       </c>
       <c r="Q4">
-        <v>1.564844889891681E-09</v>
+        <v>1.56487743476854E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
       </c>
       <c r="S4">
-        <v>179.9999999984265</v>
+        <v>179.9999999984264</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -923,22 +923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000113265527</v>
+        <v>0.9526279644483023</v>
       </c>
       <c r="O5">
-        <v>0.5500000124822031</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.100000023808756</v>
+        <v>0.9526279651154544</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999918184</v>
+        <v>2.726207470691168E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999918195</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.508882185309607E-13</v>
+        <v>179.9999999972651</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -982,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000113265527</v>
+        <v>0.9526279644483023</v>
       </c>
       <c r="O6">
-        <v>0.5500000124822031</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.100000023808756</v>
+        <v>0.9526279651154544</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999918184</v>
+        <v>2.726217007529421E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999918195</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.57565651482851E-13</v>
+        <v>179.9999999972651</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1098,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632983</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -1119,10 +1119,10 @@
         <v>0.8960735769153692</v>
       </c>
       <c r="Q2">
-        <v>5.766209884997124</v>
+        <v>5.766209884997123</v>
       </c>
       <c r="R2">
-        <v>-121.3466079962483</v>
+        <v>-121.3466079962484</v>
       </c>
       <c r="S2">
         <v>173.4315681772755</v>
@@ -1172,13 +1172,13 @@
         <v>1.02022644131502</v>
       </c>
       <c r="O3">
-        <v>0.2400406981630185</v>
+        <v>0.2400406981630186</v>
       </c>
       <c r="P3">
-        <v>0.8960735770061729</v>
+        <v>0.8960735770061726</v>
       </c>
       <c r="Q3">
-        <v>5.766209884977178</v>
+        <v>5.766209884977173</v>
       </c>
       <c r="R3">
         <v>-121.3466079609364</v>
@@ -1231,19 +1231,19 @@
         <v>1.020226441292307</v>
       </c>
       <c r="O4">
-        <v>0.2400406981651692</v>
+        <v>0.2400406981651693</v>
       </c>
       <c r="P4">
-        <v>0.8960735770323212</v>
+        <v>0.8960735770323209</v>
       </c>
       <c r="Q4">
-        <v>5.766209886018069</v>
+        <v>5.766209886018059</v>
       </c>
       <c r="R4">
         <v>-121.3466079469509</v>
       </c>
       <c r="S4">
-        <v>173.4315681777209</v>
+        <v>173.4315681777208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1287,22 +1287,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6816683455742605</v>
+        <v>1.020226441141183</v>
       </c>
       <c r="O5">
-        <v>0.4761907158671915</v>
+        <v>0.2400406979978038</v>
       </c>
       <c r="P5">
-        <v>1.100000023812009</v>
+        <v>0.8960735771819658</v>
       </c>
       <c r="Q5">
-        <v>-164.9034422503122</v>
+        <v>5.766209886546458</v>
       </c>
       <c r="R5">
-        <v>158.1097491771482</v>
+        <v>-121.3466078867097</v>
       </c>
       <c r="S5">
-        <v>9.34840613261896E-14</v>
+        <v>173.4315681791973</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6816683455742605</v>
+        <v>1.020226441141183</v>
       </c>
       <c r="O6">
-        <v>0.4761907158671914</v>
+        <v>0.2400406979978037</v>
       </c>
       <c r="P6">
-        <v>1.100000023812009</v>
+        <v>0.8960735771819658</v>
       </c>
       <c r="Q6">
-        <v>-164.9034422503122</v>
+        <v>5.766209886546458</v>
       </c>
       <c r="R6">
-        <v>158.1097491771482</v>
+        <v>-121.3466078867097</v>
       </c>
       <c r="S6">
-        <v>8.847598661228659E-14</v>
+        <v>173.4315681791973</v>
       </c>
     </row>
   </sheetData>
@@ -1465,10 +1465,10 @@
         <v>1.324394473632982</v>
       </c>
       <c r="K2">
-        <v>13.24394453600777</v>
+        <v>13.24394453600776</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -1483,10 +1483,10 @@
         <v>0.8960735769153692</v>
       </c>
       <c r="Q2">
-        <v>5.766209884997122</v>
+        <v>5.766209884997124</v>
       </c>
       <c r="R2">
-        <v>-121.3466079962484</v>
+        <v>-121.3466079962483</v>
       </c>
       <c r="S2">
         <v>173.4315681772755</v>
@@ -1536,19 +1536,19 @@
         <v>1.02022644131502</v>
       </c>
       <c r="O3">
-        <v>0.2400406981630182</v>
+        <v>0.2400406981630187</v>
       </c>
       <c r="P3">
-        <v>0.8960735770061725</v>
+        <v>0.8960735770061727</v>
       </c>
       <c r="Q3">
-        <v>5.766209884977165</v>
+        <v>5.766209884977185</v>
       </c>
       <c r="R3">
-        <v>-121.3466079609365</v>
+        <v>-121.3466079609363</v>
       </c>
       <c r="S3">
-        <v>173.4315681785684</v>
+        <v>173.4315681785683</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1595,19 +1595,19 @@
         <v>1.020226441292307</v>
       </c>
       <c r="O4">
-        <v>0.2400406981651687</v>
+        <v>0.2400406981651695</v>
       </c>
       <c r="P4">
-        <v>0.8960735770323208</v>
+        <v>0.8960735770323212</v>
       </c>
       <c r="Q4">
-        <v>5.766209886018052</v>
+        <v>5.766209886018078</v>
       </c>
       <c r="R4">
-        <v>-121.346607946951</v>
+        <v>-121.3466079469508</v>
       </c>
       <c r="S4">
-        <v>173.4315681777209</v>
+        <v>173.4315681777208</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6816683455620866</v>
+        <v>1.020226441133987</v>
       </c>
       <c r="O5">
-        <v>0.4761907158785915</v>
+        <v>0.240040697989834</v>
       </c>
       <c r="P5">
-        <v>1.100000023812008</v>
+        <v>0.8960735771890919</v>
       </c>
       <c r="Q5">
-        <v>-164.9034422500781</v>
+        <v>5.766209886571636</v>
       </c>
       <c r="R5">
-        <v>158.1097491777616</v>
+        <v>-121.346607883841</v>
       </c>
       <c r="S5">
-        <v>1.001614942780603E-13</v>
+        <v>173.4315681792677</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1710,22 +1710,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6816683455620866</v>
+        <v>1.020226441133987</v>
       </c>
       <c r="O6">
-        <v>0.4761907158785915</v>
+        <v>0.2400406979898341</v>
       </c>
       <c r="P6">
-        <v>1.100000023812008</v>
+        <v>0.896073577189092</v>
       </c>
       <c r="Q6">
-        <v>-164.9034422500781</v>
+        <v>5.76620988657164</v>
       </c>
       <c r="R6">
-        <v>158.1097491777617</v>
+        <v>-121.3466078838409</v>
       </c>
       <c r="S6">
-        <v>9.682277780212496E-14</v>
+        <v>173.4315681792677</v>
       </c>
     </row>
   </sheetData>
@@ -1805,19 +1805,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="D2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="G2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="H2">
         <v>1.504993724976268</v>
@@ -1826,7 +1826,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -1838,22 +1838,22 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.8660254037845059</v>
+        <v>0.8660254037845061</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8660254037849899</v>
+        <v>0.86602540378499</v>
       </c>
       <c r="Q2">
-        <v>1.719844818563817E-10</v>
+        <v>1.719950444124671E-10</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999998194</v>
+        <v>179.9999999998193</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660254036789677</v>
+        <v>0.8660254036789681</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>0.8660254038905285</v>
       </c>
       <c r="Q3">
-        <v>4.106868843330489E-10</v>
+        <v>4.106872987876952E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1956,16 +1956,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660254036546302</v>
+        <v>0.8660254036546307</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254039148659</v>
+        <v>0.8660254039148664</v>
       </c>
       <c r="Q4">
-        <v>3.135400462610209E-09</v>
+        <v>3.135402754256373E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2015,22 +2015,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999994714411</v>
+        <v>0.866025403479513</v>
       </c>
       <c r="O5">
-        <v>0.5000000005289075</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.000000000000349</v>
+        <v>0.8660254040899842</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999870976</v>
+        <v>4.299814745297476E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999870987</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.619059950634588E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2074,22 +2074,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999994714411</v>
+        <v>0.8660254034795127</v>
       </c>
       <c r="O6">
-        <v>0.5000000005289074</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.000000000000348</v>
+        <v>0.866025404089984</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999870976</v>
+        <v>4.299811133944751E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999870987</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.582334068604298E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
   </sheetData>
@@ -2169,19 +2169,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="D2">
-        <v>3.636363763754282</v>
+        <v>3.63636376375428</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="G2">
-        <v>230.9401157662429</v>
+        <v>230.9401157662428</v>
       </c>
       <c r="H2">
         <v>1.504993724976268</v>
@@ -2190,7 +2190,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -2202,22 +2202,22 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.8660254037845059</v>
+        <v>0.8660254037845061</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8660254037849899</v>
+        <v>0.86602540378499</v>
       </c>
       <c r="Q2">
-        <v>1.719844818563817E-10</v>
+        <v>1.719950444124671E-10</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
       <c r="S2">
-        <v>179.9999999998194</v>
+        <v>179.9999999998193</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660254036789677</v>
+        <v>0.8660254036789681</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -2270,7 +2270,7 @@
         <v>0.8660254038905285</v>
       </c>
       <c r="Q3">
-        <v>4.106868843330489E-10</v>
+        <v>4.106872987876952E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2320,16 +2320,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660254036546302</v>
+        <v>0.8660254036546307</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8660254039148659</v>
+        <v>0.8660254039148664</v>
       </c>
       <c r="Q4">
-        <v>3.135400462610209E-09</v>
+        <v>3.135402754256373E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2379,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.4999999994714411</v>
+        <v>0.866025403479513</v>
       </c>
       <c r="O5">
-        <v>0.5000000005289075</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.000000000000349</v>
+        <v>0.8660254040899842</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999870976</v>
+        <v>4.299814745297476E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999870987</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.619059950634588E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2438,22 +2438,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.4999999994714411</v>
+        <v>0.8660254034795127</v>
       </c>
       <c r="O6">
-        <v>0.5000000005289074</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.000000000000348</v>
+        <v>0.866025404089984</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999870976</v>
+        <v>4.299811133944751E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999870987</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.582334068604298E-13</v>
+        <v>179.9999999956915</v>
       </c>
     </row>
   </sheetData>
@@ -2554,7 +2554,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -2569,19 +2569,19 @@
         <v>0.9220324944339027</v>
       </c>
       <c r="O2">
-        <v>0.1964063473242865</v>
+        <v>0.1964063473242864</v>
       </c>
       <c r="P2">
         <v>0.8180121061818276</v>
       </c>
       <c r="Q2">
-        <v>5.173976904115783</v>
+        <v>5.173976904115774</v>
       </c>
       <c r="R2">
         <v>-122.1449202961592</v>
       </c>
       <c r="S2">
-        <v>174.1659345853096</v>
+        <v>174.1659345853095</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2625,19 +2625,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9220324943451749</v>
+        <v>0.9220324943451751</v>
       </c>
       <c r="O3">
-        <v>0.1964063472166725</v>
+        <v>0.1964063472166724</v>
       </c>
       <c r="P3">
-        <v>0.8180121062689192</v>
+        <v>0.8180121062689195</v>
       </c>
       <c r="Q3">
-        <v>5.173976904114572</v>
+        <v>5.173976904114554</v>
       </c>
       <c r="R3">
-        <v>-122.1449202549968</v>
+        <v>-122.1449202549969</v>
       </c>
       <c r="S3">
         <v>174.1659345864976</v>
@@ -2684,22 +2684,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9220324943235482</v>
+        <v>0.9220324943235484</v>
       </c>
       <c r="O4">
-        <v>0.1964063472443383</v>
+        <v>0.1964063472443382</v>
       </c>
       <c r="P4">
-        <v>0.8180121062966175</v>
+        <v>0.8180121062966177</v>
       </c>
       <c r="Q4">
-        <v>5.17397690621992</v>
+        <v>5.173976906219901</v>
       </c>
       <c r="R4">
         <v>-122.1449202329783</v>
       </c>
       <c r="S4">
-        <v>174.1659345844575</v>
+        <v>174.1659345844574</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2743,22 +2743,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6078088901105025</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O5">
-        <v>0.434087010711988</v>
+        <v>0.1964063470808816</v>
       </c>
       <c r="P5">
-        <v>1.000000000005794</v>
+        <v>0.8180121064433186</v>
       </c>
       <c r="Q5">
-        <v>-166.2935793191085</v>
+        <v>5.173976906823905</v>
       </c>
       <c r="R5">
-        <v>160.6235536416969</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S5">
-        <v>1.487398222218704E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2802,22 +2802,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6078088901105025</v>
+        <v>0.9220324941759886</v>
       </c>
       <c r="O6">
-        <v>0.434087010711988</v>
+        <v>0.1964063470808814</v>
       </c>
       <c r="P6">
-        <v>1.000000000005794</v>
+        <v>0.8180121064433186</v>
       </c>
       <c r="Q6">
-        <v>-166.2935793191086</v>
+        <v>5.173976906823902</v>
       </c>
       <c r="R6">
-        <v>160.6235536416969</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S6">
-        <v>1.450672340188613E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
   </sheetData>
@@ -2918,7 +2918,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -2933,19 +2933,19 @@
         <v>0.9220324944339027</v>
       </c>
       <c r="O2">
-        <v>0.1964063473242865</v>
+        <v>0.1964063473242864</v>
       </c>
       <c r="P2">
         <v>0.8180121061818276</v>
       </c>
       <c r="Q2">
-        <v>5.173976904115783</v>
+        <v>5.173976904115774</v>
       </c>
       <c r="R2">
         <v>-122.1449202961592</v>
       </c>
       <c r="S2">
-        <v>174.1659345853096</v>
+        <v>174.1659345853095</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2989,19 +2989,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9220324943451749</v>
+        <v>0.9220324943451751</v>
       </c>
       <c r="O3">
-        <v>0.1964063472166725</v>
+        <v>0.1964063472166724</v>
       </c>
       <c r="P3">
-        <v>0.8180121062689192</v>
+        <v>0.8180121062689195</v>
       </c>
       <c r="Q3">
-        <v>5.173976904114572</v>
+        <v>5.173976904114554</v>
       </c>
       <c r="R3">
-        <v>-122.1449202549968</v>
+        <v>-122.1449202549969</v>
       </c>
       <c r="S3">
         <v>174.1659345864976</v>
@@ -3048,22 +3048,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9220324943235482</v>
+        <v>0.9220324943235484</v>
       </c>
       <c r="O4">
-        <v>0.1964063472443383</v>
+        <v>0.1964063472443382</v>
       </c>
       <c r="P4">
-        <v>0.8180121062966175</v>
+        <v>0.8180121062966177</v>
       </c>
       <c r="Q4">
-        <v>5.17397690621992</v>
+        <v>5.173976906219901</v>
       </c>
       <c r="R4">
         <v>-122.1449202329783</v>
       </c>
       <c r="S4">
-        <v>174.1659345844575</v>
+        <v>174.1659345844574</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3107,22 +3107,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6078088901105025</v>
+        <v>0.9220324941759883</v>
       </c>
       <c r="O5">
-        <v>0.434087010711988</v>
+        <v>0.1964063470808816</v>
       </c>
       <c r="P5">
-        <v>1.000000000005794</v>
+        <v>0.8180121064433186</v>
       </c>
       <c r="Q5">
-        <v>-166.2935793191085</v>
+        <v>5.173976906823905</v>
       </c>
       <c r="R5">
-        <v>160.6235536416969</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S5">
-        <v>1.487398222218704E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3166,22 +3166,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6078088901105025</v>
+        <v>0.9220324941759886</v>
       </c>
       <c r="O6">
-        <v>0.434087010711988</v>
+        <v>0.1964063470808814</v>
       </c>
       <c r="P6">
-        <v>1.000000000005794</v>
+        <v>0.8180121064433186</v>
       </c>
       <c r="Q6">
-        <v>-166.2935793191086</v>
+        <v>5.173976906823902</v>
       </c>
       <c r="R6">
-        <v>160.6235536416969</v>
+        <v>-122.1449201610731</v>
       </c>
       <c r="S6">
-        <v>1.450672340188613E-13</v>
+        <v>174.1659345857627</v>
       </c>
     </row>
   </sheetData>
@@ -3285,7 +3285,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632983</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -3303,7 +3303,7 @@
         <v>1.100000023884844</v>
       </c>
       <c r="P2">
-        <v>0.6350853099409384</v>
+        <v>0.6350853099409385</v>
       </c>
       <c r="Q2">
         <v>59.99999999685334</v>
@@ -3312,7 +3312,7 @@
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>119.9999999996536</v>
+        <v>119.9999999996535</v>
       </c>
       <c r="T2">
         <v>5.248639108526412</v>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853099894119</v>
+        <v>0.6350853099894115</v>
       </c>
       <c r="O3">
         <v>1.100000023884844</v>
@@ -3368,10 +3368,10 @@
         <v>0.6350853098300097</v>
       </c>
       <c r="Q3">
-        <v>60.00000000239911</v>
+        <v>60.00000000239913</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999584</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S3">
         <v>120.0000000058974</v>
@@ -3421,16 +3421,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853100298057</v>
+        <v>0.6350853100298054</v>
       </c>
       <c r="O4">
         <v>1.100000023884844</v>
       </c>
       <c r="P4">
-        <v>0.635085309816861</v>
+        <v>0.6350853098168611</v>
       </c>
       <c r="Q4">
-        <v>60.00000000166486</v>
+        <v>60.0000000016649</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
@@ -3483,22 +3483,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9701088353190509</v>
+        <v>0.6350853102238362</v>
       </c>
       <c r="O5">
-        <v>0.9701088349395171</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P5">
-        <v>0.3666666747102745</v>
+        <v>0.6350853096441128</v>
       </c>
       <c r="Q5">
-        <v>-100.8933946493481</v>
+        <v>60.00000000955429</v>
       </c>
       <c r="R5">
-        <v>100.8933946536594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>6.039343466929187E-08</v>
+        <v>120.0000000206356</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3545,22 +3545,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9701088353190509</v>
+        <v>0.6350853102238361</v>
       </c>
       <c r="O6">
-        <v>0.9701088349395169</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P6">
-        <v>0.3666666747102743</v>
+        <v>0.6350853096441129</v>
       </c>
       <c r="Q6">
-        <v>-100.8933946493481</v>
+        <v>60.00000000955429</v>
       </c>
       <c r="R6">
-        <v>100.8933946536594</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>6.039344468544132E-08</v>
+        <v>120.0000000206356</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -3670,10 +3670,10 @@
         <v>1.324394473632982</v>
       </c>
       <c r="K2">
-        <v>13.24394453600777</v>
+        <v>13.24394453600776</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -3685,16 +3685,16 @@
         <v>1.100000023884844</v>
       </c>
       <c r="P2">
-        <v>0.6350853099409385</v>
+        <v>0.6350853099409386</v>
       </c>
       <c r="Q2">
-        <v>59.99999999685334</v>
+        <v>59.99999999685333</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>119.9999999996535</v>
+        <v>119.9999999996536</v>
       </c>
       <c r="T2">
         <v>5.248639108526412</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853099894116</v>
+        <v>0.6350853099894119</v>
       </c>
       <c r="O3">
         <v>1.100000023884844</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853100298055</v>
+        <v>0.6350853100298056</v>
       </c>
       <c r="O4">
         <v>1.100000023884844</v>
@@ -3812,13 +3812,13 @@
         <v>0.6350853098168615</v>
       </c>
       <c r="Q4">
-        <v>60.00000000166487</v>
+        <v>60.00000000166486</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>120.0000000094205</v>
+        <v>120.0000000094206</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9701088353248785</v>
+        <v>0.635085310233076</v>
       </c>
       <c r="O5">
-        <v>0.970108834933911</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P5">
-        <v>0.3666666747114445</v>
+        <v>0.6350853096358874</v>
       </c>
       <c r="Q5">
-        <v>-100.893394649317</v>
+        <v>60.00000000992994</v>
       </c>
       <c r="R5">
-        <v>100.8933946537583</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>6.221285819597757E-08</v>
+        <v>120.0000000211697</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3927,22 +3927,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9701088353248785</v>
+        <v>0.635085310233076</v>
       </c>
       <c r="O6">
-        <v>0.970108834933911</v>
+        <v>1.100000023884844</v>
       </c>
       <c r="P6">
-        <v>0.3666666747114444</v>
+        <v>0.6350853096358874</v>
       </c>
       <c r="Q6">
-        <v>-100.893394649317</v>
+        <v>60.00000000992993</v>
       </c>
       <c r="R6">
-        <v>100.8933946537583</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>6.221285819597758E-08</v>
+        <v>120.0000000211697</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632983</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -4061,7 +4061,7 @@
         <v>13.24394453563996</v>
       </c>
       <c r="N2">
-        <v>0.6918398877278029</v>
+        <v>0.6918398877278028</v>
       </c>
       <c r="O2">
         <v>1.100000023874158</v>
@@ -4070,7 +4070,7 @@
         <v>0.8378427578966809</v>
       </c>
       <c r="Q2">
-        <v>40.40951795604942</v>
+        <v>40.40951795604943</v>
       </c>
       <c r="R2">
         <v>-89.99999999999653</v>
@@ -4123,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6918398877714432</v>
+        <v>0.6918398877714429</v>
       </c>
       <c r="O3">
         <v>1.100000023874165</v>
@@ -4132,13 +4132,13 @@
         <v>0.83784275781675</v>
       </c>
       <c r="Q3">
-        <v>40.40951796258038</v>
+        <v>40.40951796258039</v>
       </c>
       <c r="R3">
         <v>-89.99999999999616</v>
       </c>
       <c r="S3">
-        <v>128.9574716984652</v>
+        <v>128.9574716984651</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6918398877978509</v>
+        <v>0.6918398877978506</v>
       </c>
       <c r="O4">
         <v>1.100000023874165</v>
@@ -4194,7 +4194,7 @@
         <v>0.8378427578056246</v>
       </c>
       <c r="Q4">
-        <v>40.4095179634466</v>
+        <v>40.40951796344662</v>
       </c>
       <c r="R4">
         <v>-89.99999999999616</v>
@@ -4247,22 +4247,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9443347710364152</v>
+        <v>0.6918398878771924</v>
       </c>
       <c r="O5">
-        <v>1.05598589759888</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P5">
-        <v>0.6194744497252986</v>
+        <v>0.8378427576802557</v>
       </c>
       <c r="Q5">
-        <v>-108.7881138020852</v>
+        <v>40.40951797366601</v>
       </c>
       <c r="R5">
-        <v>106.7392371182271</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S5">
-        <v>-10.90775016075237</v>
+        <v>128.9574717054625</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4309,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9443347710364152</v>
+        <v>0.6918398878771924</v>
       </c>
       <c r="O6">
-        <v>1.05598589759888</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P6">
-        <v>0.6194744497252986</v>
+        <v>0.8378427576802556</v>
       </c>
       <c r="Q6">
-        <v>-108.7881138020852</v>
+        <v>40.40951797366601</v>
       </c>
       <c r="R6">
-        <v>106.7392371182271</v>
+        <v>-89.99999999999616</v>
       </c>
       <c r="S6">
-        <v>-10.90775016075236</v>
+        <v>128.9574717054625</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>1000.000056712887</v>
       </c>
       <c r="D2">
-        <v>1.324394473835048</v>
+        <v>1.324394473835047</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
@@ -4582,10 +4582,10 @@
         <v>1.324394473632982</v>
       </c>
       <c r="K2">
-        <v>13.24394453600777</v>
+        <v>13.24394453600776</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -4597,13 +4597,13 @@
         <v>1.100000023874158</v>
       </c>
       <c r="P2">
-        <v>0.8378427578966811</v>
+        <v>0.8378427578966813</v>
       </c>
       <c r="Q2">
         <v>40.40951795604942</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S2">
         <v>128.9574716956184</v>
@@ -4653,22 +4653,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.691839887771443</v>
+        <v>0.6918398877714431</v>
       </c>
       <c r="O3">
         <v>1.100000023874165</v>
       </c>
       <c r="P3">
-        <v>0.8378427578167501</v>
+        <v>0.8378427578167503</v>
       </c>
       <c r="Q3">
-        <v>40.40951796258037</v>
+        <v>40.40951796258038</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999616</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S3">
-        <v>128.9574716984651</v>
+        <v>128.9574716984652</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4715,13 +4715,13 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6918398877978506</v>
+        <v>0.6918398877978508</v>
       </c>
       <c r="O4">
         <v>1.100000023874165</v>
       </c>
       <c r="P4">
-        <v>0.8378427578056247</v>
+        <v>0.837842757805625</v>
       </c>
       <c r="Q4">
         <v>40.4095179634466</v>
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9443347710400261</v>
+        <v>0.6918398878809707</v>
       </c>
       <c r="O5">
-        <v>1.055985897594897</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P5">
-        <v>0.6194744497227285</v>
+        <v>0.8378427576742861</v>
       </c>
       <c r="Q5">
-        <v>-108.7881138019762</v>
+        <v>40.40951797415263</v>
       </c>
       <c r="R5">
-        <v>106.7392371182616</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S5">
-        <v>-10.90775016004519</v>
+        <v>128.9574717057106</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4839,22 +4839,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9443347710400262</v>
+        <v>0.6918398878809708</v>
       </c>
       <c r="O6">
-        <v>1.055985897594897</v>
+        <v>1.100000023874165</v>
       </c>
       <c r="P6">
-        <v>0.6194744497227285</v>
+        <v>0.8378427576742861</v>
       </c>
       <c r="Q6">
-        <v>-108.7881138019762</v>
+        <v>40.40951797415262</v>
       </c>
       <c r="R6">
-        <v>106.7392371182616</v>
+        <v>-89.99999999999615</v>
       </c>
       <c r="S6">
-        <v>-10.90775016004519</v>
+        <v>128.9574717057106</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4961,7 +4961,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -4973,7 +4973,7 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502691155638</v>
+        <v>0.5773502691155639</v>
       </c>
       <c r="O2">
         <v>0.9999999999962956</v>
@@ -4982,7 +4982,7 @@
         <v>0.5773502692541782</v>
       </c>
       <c r="Q2">
-        <v>59.99999999647621</v>
+        <v>59.99999999647622</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
@@ -5035,22 +5035,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502692231759</v>
+        <v>0.5773502692231761</v>
       </c>
       <c r="O3">
-        <v>0.9999999999962955</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P3">
-        <v>0.5773502691507324</v>
+        <v>0.5773502691507321</v>
       </c>
       <c r="Q3">
-        <v>60.00000000216503</v>
+        <v>60.00000000216507</v>
       </c>
       <c r="R3">
         <v>-89.99999999999582</v>
       </c>
       <c r="S3">
-        <v>120.0000000019794</v>
+        <v>120.0000000019795</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5097,22 +5097,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502692712909</v>
+        <v>0.5773502692712913</v>
       </c>
       <c r="O4">
         <v>0.9999999999962956</v>
       </c>
       <c r="P4">
-        <v>0.5773502691501727</v>
+        <v>0.5773502691501723</v>
       </c>
       <c r="Q4">
-        <v>59.9999999994724</v>
+        <v>59.99999999947243</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>120.0000000074609</v>
+        <v>120.000000007461</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5159,22 +5159,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8819171038465827</v>
+        <v>0.5773502694565704</v>
       </c>
       <c r="O5">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P5">
-        <v>0.3333333334093276</v>
+        <v>0.5773502689852159</v>
       </c>
       <c r="Q5">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775933</v>
       </c>
       <c r="R5">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>5.401442020840415E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5221,22 +5221,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8819171038465828</v>
+        <v>0.5773502694565704</v>
       </c>
       <c r="O6">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P6">
-        <v>0.3333333334093277</v>
+        <v>0.5773502689852159</v>
       </c>
       <c r="Q6">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775933</v>
       </c>
       <c r="R6">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>5.401442020840414E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -5355,7 +5355,7 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502691155638</v>
+        <v>0.5773502691155639</v>
       </c>
       <c r="O2">
         <v>0.9999999999962956</v>
@@ -5364,7 +5364,7 @@
         <v>0.5773502692541782</v>
       </c>
       <c r="Q2">
-        <v>59.99999999647621</v>
+        <v>59.99999999647622</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502692231759</v>
+        <v>0.5773502692231761</v>
       </c>
       <c r="O3">
-        <v>0.9999999999962955</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P3">
-        <v>0.5773502691507324</v>
+        <v>0.5773502691507321</v>
       </c>
       <c r="Q3">
-        <v>60.00000000216503</v>
+        <v>60.00000000216507</v>
       </c>
       <c r="R3">
         <v>-89.99999999999582</v>
       </c>
       <c r="S3">
-        <v>120.0000000019794</v>
+        <v>120.0000000019795</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5479,22 +5479,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502692712909</v>
+        <v>0.5773502692712913</v>
       </c>
       <c r="O4">
         <v>0.9999999999962956</v>
       </c>
       <c r="P4">
-        <v>0.5773502691501727</v>
+        <v>0.5773502691501723</v>
       </c>
       <c r="Q4">
-        <v>59.9999999994724</v>
+        <v>59.99999999947243</v>
       </c>
       <c r="R4">
         <v>-89.99999999999582</v>
       </c>
       <c r="S4">
-        <v>120.0000000074609</v>
+        <v>120.000000007461</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5541,22 +5541,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8819171038465827</v>
+        <v>0.5773502694565704</v>
       </c>
       <c r="O5">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P5">
-        <v>0.3333333334093276</v>
+        <v>0.5773502689852159</v>
       </c>
       <c r="Q5">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775933</v>
       </c>
       <c r="R5">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S5">
-        <v>5.401442020840415E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8819171038465828</v>
+        <v>0.5773502694565704</v>
       </c>
       <c r="O6">
-        <v>0.8819171035379949</v>
+        <v>0.9999999999962956</v>
       </c>
       <c r="P6">
-        <v>0.3333333334093277</v>
+        <v>0.5773502689852159</v>
       </c>
       <c r="Q6">
-        <v>-100.8933946496616</v>
+        <v>60.00000000775933</v>
       </c>
       <c r="R6">
-        <v>100.8933946535174</v>
+        <v>-89.99999999999582</v>
       </c>
       <c r="S6">
-        <v>5.401442020840414E-08</v>
+        <v>120.0000000192411</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5725,7 +5725,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -5737,16 +5737,16 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.6184267549947473</v>
+        <v>0.6184267549947475</v>
       </c>
       <c r="O2">
         <v>0.9999999999908645</v>
       </c>
       <c r="P2">
-        <v>0.747299752735181</v>
+        <v>0.7472997527351807</v>
       </c>
       <c r="Q2">
-        <v>41.77463363119257</v>
+        <v>41.77463363119259</v>
       </c>
       <c r="R2">
         <v>-89.99999999999652</v>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6184267550404211</v>
+        <v>0.6184267550404213</v>
       </c>
       <c r="O3">
         <v>0.9999999999908707</v>
       </c>
       <c r="P3">
-        <v>0.7472997526577979</v>
+        <v>0.7472997526577976</v>
       </c>
       <c r="Q3">
-        <v>41.77463363810639</v>
+        <v>41.7746336381064</v>
       </c>
       <c r="R3">
         <v>-89.99999999999613</v>
@@ -5861,19 +5861,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6184267550800499</v>
+        <v>0.6184267550800504</v>
       </c>
       <c r="O4">
         <v>0.9999999999908707</v>
       </c>
       <c r="P4">
-        <v>0.7472997526545254</v>
+        <v>0.7472997526545251</v>
       </c>
       <c r="Q4">
         <v>41.774633638175</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999612</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S4">
         <v>128.1091583258393</v>
@@ -5923,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8576025464121366</v>
+        <v>0.6184267551642111</v>
       </c>
       <c r="O5">
-        <v>0.9547184905727351</v>
+        <v>0.9999999999908707</v>
       </c>
       <c r="P5">
-        <v>0.5421614591269468</v>
+        <v>0.7472997525303006</v>
       </c>
       <c r="Q5">
-        <v>-108.0887396139939</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R5">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S5">
-        <v>-10.80277167314921</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5985,22 +5985,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8576025464121364</v>
+        <v>0.618426755164211</v>
       </c>
       <c r="O6">
-        <v>0.9547184905727348</v>
+        <v>0.9999999999908707</v>
       </c>
       <c r="P6">
-        <v>0.5421614591269467</v>
+        <v>0.7472997525303006</v>
       </c>
       <c r="Q6">
-        <v>-108.0887396139939</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R6">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S6">
-        <v>-10.80277167314921</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -6119,16 +6119,16 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.6184267549947473</v>
+        <v>0.6184267549947475</v>
       </c>
       <c r="O2">
         <v>0.9999999999908645</v>
       </c>
       <c r="P2">
-        <v>0.747299752735181</v>
+        <v>0.7472997527351807</v>
       </c>
       <c r="Q2">
-        <v>41.77463363119257</v>
+        <v>41.77463363119259</v>
       </c>
       <c r="R2">
         <v>-89.99999999999652</v>
@@ -6181,16 +6181,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6184267550404211</v>
+        <v>0.6184267550404213</v>
       </c>
       <c r="O3">
         <v>0.9999999999908707</v>
       </c>
       <c r="P3">
-        <v>0.7472997526577979</v>
+        <v>0.7472997526577976</v>
       </c>
       <c r="Q3">
-        <v>41.77463363810639</v>
+        <v>41.7746336381064</v>
       </c>
       <c r="R3">
         <v>-89.99999999999613</v>
@@ -6243,19 +6243,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6184267550800499</v>
+        <v>0.6184267550800504</v>
       </c>
       <c r="O4">
         <v>0.9999999999908707</v>
       </c>
       <c r="P4">
-        <v>0.7472997526545254</v>
+        <v>0.7472997526545251</v>
       </c>
       <c r="Q4">
         <v>41.774633638175</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999612</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S4">
         <v>128.1091583258393</v>
@@ -6305,22 +6305,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8576025464121366</v>
+        <v>0.6184267551642111</v>
       </c>
       <c r="O5">
-        <v>0.9547184905727351</v>
+        <v>0.9999999999908707</v>
       </c>
       <c r="P5">
-        <v>0.5421614591269468</v>
+        <v>0.7472997525303006</v>
       </c>
       <c r="Q5">
-        <v>-108.0887396139939</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R5">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S5">
-        <v>-10.80277167314921</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6367,22 +6367,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8576025464121364</v>
+        <v>0.618426755164211</v>
       </c>
       <c r="O6">
-        <v>0.9547184905727348</v>
+        <v>0.9999999999908707</v>
       </c>
       <c r="P6">
-        <v>0.5421614591269467</v>
+        <v>0.7472997525303006</v>
       </c>
       <c r="Q6">
-        <v>-108.0887396139939</v>
+        <v>41.77463364920821</v>
       </c>
       <c r="R6">
-        <v>106.1949204578978</v>
+        <v>-89.99999999999613</v>
       </c>
       <c r="S6">
-        <v>-10.80277167314921</v>
+        <v>128.109158331695</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>5.24863910873685</v>
       </c>
       <c r="D2">
-        <v>5.248639107970815</v>
+        <v>5.248639107970814</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632983</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -6507,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.6350853098507082</v>
+        <v>0.6350853098507083</v>
       </c>
       <c r="Q2">
-        <v>-4.877409581425555E-09</v>
+        <v>-4.877410550668154E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>179.999999996043</v>
       </c>
       <c r="T2">
-        <v>5.248639108420278</v>
+        <v>5.248639108420276</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -6563,16 +6563,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6350853097237747</v>
+        <v>0.6350853097237746</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.6350853099661095</v>
+        <v>0.6350853099661091</v>
       </c>
       <c r="Q3">
-        <v>1.367233864006146E-09</v>
+        <v>1.367217469331785E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -6625,16 +6625,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853097106263</v>
+        <v>0.6350853097106257</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.6350853100065035</v>
+        <v>0.635085310006503</v>
       </c>
       <c r="Q4">
-        <v>4.890367151991687E-09</v>
+        <v>4.890335861589059E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -6687,22 +6687,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.3666666740374639</v>
+        <v>0.6350853095378777</v>
       </c>
       <c r="O5">
-        <v>0.3666666751852972</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7333333492227611</v>
+        <v>0.6350853102005337</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999765368</v>
+        <v>1.610538692517103E-08</v>
       </c>
       <c r="R5">
-        <v>-179.999999998587</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.243077762664011E-08</v>
+        <v>-179.9999999912407</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6749,22 +6749,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3666666740374638</v>
+        <v>0.6350853095378778</v>
       </c>
       <c r="O6">
-        <v>0.3666666751852972</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7333333492227611</v>
+        <v>0.6350853102005337</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999765367</v>
+        <v>1.610539758873742E-08</v>
       </c>
       <c r="R6">
-        <v>-179.9999999985871</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.243078263471482E-08</v>
+        <v>-179.9999999912407</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>5.248639108736849</v>
+        <v>5.24863910873685</v>
       </c>
       <c r="D2">
         <v>5.248639107970815</v>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>333.3333522539259</v>
+        <v>333.333352253926</v>
       </c>
       <c r="G2">
         <v>333.3333522052762</v>
@@ -6874,10 +6874,10 @@
         <v>1.324394473632982</v>
       </c>
       <c r="K2">
-        <v>13.24394453600777</v>
+        <v>13.24394453600776</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -6892,7 +6892,7 @@
         <v>0.6350853098507082</v>
       </c>
       <c r="Q2">
-        <v>-4.877402829356387E-09</v>
+        <v>-4.877420177836092E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -6951,16 +6951,16 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.635085309966109</v>
+        <v>0.6350853099661096</v>
       </c>
       <c r="Q3">
-        <v>1.367233788204657E-09</v>
+        <v>1.367251651487784E-09</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>-179.9999999983958</v>
+        <v>-179.9999999983959</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7007,16 +7007,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6350853097106259</v>
+        <v>0.6350853097106262</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.635085310006503</v>
+        <v>0.6350853100065036</v>
       </c>
       <c r="Q4">
-        <v>4.890346716918471E-09</v>
+        <v>4.890377182507741E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -7069,22 +7069,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.3666666740226305</v>
+        <v>0.6350853095296519</v>
       </c>
       <c r="O5">
-        <v>0.3666666752007153</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.7333333492233458</v>
+        <v>0.6350853102097739</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999758444</v>
+        <v>1.663946770752399E-08</v>
       </c>
       <c r="R5">
-        <v>-179.9999999983696</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.288567607710863E-08</v>
+        <v>-179.999999990865</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7131,22 +7131,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3666666740226305</v>
+        <v>0.6350853095296519</v>
       </c>
       <c r="O6">
-        <v>0.3666666752007152</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7333333492233457</v>
+        <v>0.6350853102097739</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999758444</v>
+        <v>1.663946355626265E-08</v>
       </c>
       <c r="R6">
-        <v>-179.9999999983696</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.288567106903392E-08</v>
+        <v>-179.999999990865</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>3.617960382593723</v>
       </c>
       <c r="D2">
-        <v>3.617960382231207</v>
+        <v>3.617960382231206</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7253,7 +7253,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632983</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -7268,22 +7268,22 @@
         <v>0.8378427578256962</v>
       </c>
       <c r="O2">
-        <v>0.4028253111898906</v>
+        <v>0.4028253111898905</v>
       </c>
       <c r="P2">
         <v>0.6918398877011797</v>
       </c>
       <c r="Q2">
-        <v>8.957471693504786</v>
+        <v>8.957471693504784</v>
       </c>
       <c r="R2">
-        <v>-115.8807585964591</v>
+        <v>-115.8807585964592</v>
       </c>
       <c r="S2">
         <v>160.4095179569557</v>
       </c>
       <c r="T2">
-        <v>3.617960382370079</v>
+        <v>3.617960382370077</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -7327,22 +7327,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8378427577457516</v>
+        <v>0.8378427577457513</v>
       </c>
       <c r="O3">
-        <v>0.4028253110952152</v>
+        <v>0.4028253110952154</v>
       </c>
       <c r="P3">
         <v>0.6918398877448089</v>
       </c>
       <c r="Q3">
-        <v>8.95747169635165</v>
+        <v>8.957471696351645</v>
       </c>
       <c r="R3">
         <v>-115.8807585788046</v>
       </c>
       <c r="S3">
-        <v>160.4095179634874</v>
+        <v>160.4095179634873</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8378427577346262</v>
+        <v>0.8378427577346261</v>
       </c>
       <c r="O4">
         <v>0.4028253110970199</v>
       </c>
       <c r="P4">
-        <v>0.6918398877712167</v>
+        <v>0.6918398877712165</v>
       </c>
       <c r="Q4">
-        <v>8.95747169813883</v>
+        <v>8.957471698138823</v>
       </c>
       <c r="R4">
         <v>-115.8807585718118</v>
@@ -7451,22 +7451,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6454597856902592</v>
+        <v>0.8378427576092572</v>
       </c>
       <c r="O5">
-        <v>0.4396365304272606</v>
+        <v>0.4028253109565874</v>
       </c>
       <c r="P5">
-        <v>0.8561498316399889</v>
+        <v>0.6918398878505583</v>
       </c>
       <c r="Q5">
-        <v>-153.840718235564</v>
+        <v>8.957471703349032</v>
       </c>
       <c r="R5">
-        <v>128.6858355816165</v>
+        <v>-115.8807585416912</v>
       </c>
       <c r="S5">
-        <v>-3.925473809326203</v>
+        <v>160.4095179745729</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7513,22 +7513,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6454597856902593</v>
+        <v>0.8378427576092572</v>
       </c>
       <c r="O6">
-        <v>0.4396365304272607</v>
+        <v>0.4028253109565874</v>
       </c>
       <c r="P6">
-        <v>0.856149831639989</v>
+        <v>0.6918398878505582</v>
       </c>
       <c r="Q6">
-        <v>-153.840718235564</v>
+        <v>8.957471703349036</v>
       </c>
       <c r="R6">
-        <v>128.6858355816165</v>
+        <v>-115.8807585416912</v>
       </c>
       <c r="S6">
-        <v>-3.925473809326209</v>
+        <v>160.4095179745729</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7617,7 +7617,7 @@
         <v>3.617960382593723</v>
       </c>
       <c r="D2">
-        <v>3.617960382231206</v>
+        <v>3.617960382231207</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7638,10 +7638,10 @@
         <v>1.324394473632982</v>
       </c>
       <c r="K2">
-        <v>13.24394453600777</v>
+        <v>13.24394453600776</v>
       </c>
       <c r="L2">
-        <v>1.324394474104424</v>
+        <v>1.324394474104425</v>
       </c>
       <c r="M2">
         <v>13.24394453563996</v>
@@ -7650,7 +7650,7 @@
         <v>0.8378427578256962</v>
       </c>
       <c r="O2">
-        <v>0.4028253111898905</v>
+        <v>0.4028253111898906</v>
       </c>
       <c r="P2">
         <v>0.6918398877011798</v>
@@ -7659,13 +7659,13 @@
         <v>8.957471693504779</v>
       </c>
       <c r="R2">
-        <v>-115.8807585964592</v>
+        <v>-115.8807585964591</v>
       </c>
       <c r="S2">
         <v>160.4095179569557</v>
       </c>
       <c r="T2">
-        <v>3.617960382370077</v>
+        <v>3.617960382370078</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -7709,19 +7709,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8378427577457515</v>
+        <v>0.8378427577457513</v>
       </c>
       <c r="O3">
-        <v>0.4028253110952151</v>
+        <v>0.4028253110952156</v>
       </c>
       <c r="P3">
-        <v>0.6918398877448089</v>
+        <v>0.6918398877448091</v>
       </c>
       <c r="Q3">
-        <v>8.957471696351631</v>
+        <v>8.957471696351663</v>
       </c>
       <c r="R3">
-        <v>-115.8807585788046</v>
+        <v>-115.8807585788045</v>
       </c>
       <c r="S3">
         <v>160.4095179634873</v>
@@ -7771,22 +7771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8378427577346257</v>
+        <v>0.8378427577346261</v>
       </c>
       <c r="O4">
-        <v>0.4028253110970196</v>
+        <v>0.4028253110970204</v>
       </c>
       <c r="P4">
-        <v>0.6918398877712165</v>
+        <v>0.6918398877712169</v>
       </c>
       <c r="Q4">
-        <v>8.957471698138811</v>
+        <v>8.957471698138841</v>
       </c>
       <c r="R4">
-        <v>-115.8807585718118</v>
+        <v>-115.8807585718117</v>
       </c>
       <c r="S4">
-        <v>160.4095179643536</v>
+        <v>160.4095179643535</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7833,22 +7833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6454597856809604</v>
+        <v>0.8378427576032873</v>
       </c>
       <c r="O5">
-        <v>0.4396365304309318</v>
+        <v>0.4028253109499004</v>
       </c>
       <c r="P5">
-        <v>0.8561498316391778</v>
+        <v>0.6918398878543368</v>
       </c>
       <c r="Q5">
-        <v>-153.8407182350992</v>
+        <v>8.957471703597154</v>
       </c>
       <c r="R5">
-        <v>128.6858355829223</v>
+        <v>-115.8807585402568</v>
       </c>
       <c r="S5">
-        <v>-3.925473809061802</v>
+        <v>160.4095179750596</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7895,22 +7895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.6454597856809604</v>
+        <v>0.8378427576032873</v>
       </c>
       <c r="O6">
-        <v>0.4396365304309317</v>
+        <v>0.4028253109499004</v>
       </c>
       <c r="P6">
-        <v>0.8561498316391778</v>
+        <v>0.6918398878543368</v>
       </c>
       <c r="Q6">
-        <v>-153.8407182350992</v>
+        <v>8.957471703597154</v>
       </c>
       <c r="R6">
-        <v>128.6858355829223</v>
+        <v>-115.8807585402568</v>
       </c>
       <c r="S6">
-        <v>-3.925473809061811</v>
+        <v>160.4095179750596</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.198911196109217</v>
+        <v>4.198911196109218</v>
       </c>
       <c r="D2">
         <v>4.198911195412808</v>
@@ -8005,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>266.6666760314689</v>
+        <v>266.666676031469</v>
       </c>
       <c r="G2">
         <v>266.666675987241</v>
@@ -8017,7 +8017,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -8029,16 +8029,16 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502691952341</v>
+        <v>0.577350269195234</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5773502691743765</v>
+        <v>0.5773502691743764</v>
       </c>
       <c r="Q2">
-        <v>-5.812885219395885E-09</v>
+        <v>-5.812891580505249E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -8047,7 +8047,7 @@
         <v>179.9999999936331</v>
       </c>
       <c r="T2">
-        <v>4.198911195821409</v>
+        <v>4.19891119582141</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502690917837</v>
+        <v>0.5773502690917839</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5773502692819935</v>
+        <v>0.5773502692819937</v>
       </c>
       <c r="Q3">
-        <v>5.928719920660776E-10</v>
+        <v>5.928523598746902E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999993227</v>
+        <v>179.9999999993228</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8153,16 +8153,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502690912237</v>
+        <v>0.577350269091224</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5773502693301086</v>
+        <v>0.577350269330109</v>
       </c>
       <c r="Q4">
-        <v>6.074372594463963E-09</v>
+        <v>6.074352101551187E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -8215,22 +8215,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.3333333328411343</v>
+        <v>0.5773502689262676</v>
       </c>
       <c r="O5">
-        <v>0.3333333338615928</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6666666667027271</v>
+        <v>0.577350269515388</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999692109</v>
+        <v>1.785448388499469E-08</v>
       </c>
       <c r="R5">
-        <v>179.9999999919939</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.139147616625086E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8277,22 +8277,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3333333328411341</v>
+        <v>0.5773502689262676</v>
       </c>
       <c r="O6">
-        <v>0.3333333338615929</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6666666667027271</v>
+        <v>0.5773502695153883</v>
       </c>
       <c r="Q6">
-        <v>-179.999999969211</v>
+        <v>1.785447762822763E-08</v>
       </c>
       <c r="R6">
-        <v>179.9999999919939</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.139147065736856E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8336,22 +8336,22 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960382498489</v>
+        <v>3.617960382498488</v>
       </c>
       <c r="C2">
-        <v>689.3140322484581</v>
+        <v>689.314032248458</v>
       </c>
       <c r="D2">
-        <v>1.324394473835047</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
       </c>
       <c r="F2">
-        <v>0.4028253111823098</v>
+        <v>0.4028253111823096</v>
       </c>
       <c r="G2">
-        <v>45.00000000004624</v>
+        <v>45.00000000004627</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8371,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.4028253110876387</v>
+        <v>0.4028253110876384</v>
       </c>
       <c r="G3">
-        <v>-25.88075857997284</v>
+        <v>-25.8807585799728</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8394,10 +8394,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.4028253110894434</v>
+        <v>0.402825311089443</v>
       </c>
       <c r="G4">
-        <v>-25.88075857298011</v>
+        <v>-25.88075857298006</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8417,10 +8417,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.4028253109490411</v>
+        <v>0.4028253109490105</v>
       </c>
       <c r="G5">
-        <v>-175.8807585428509</v>
+        <v>-25.88075854285943</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8440,10 +8440,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.4028253109490411</v>
+        <v>0.4028253109490105</v>
       </c>
       <c r="G6">
-        <v>-175.8807585428509</v>
+        <v>-25.88075854285943</v>
       </c>
     </row>
   </sheetData>
@@ -8526,7 +8526,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4.198911196109217</v>
+        <v>4.198911196109218</v>
       </c>
       <c r="D2">
         <v>4.198911195412808</v>
@@ -8535,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>266.6666760314689</v>
+        <v>266.666676031469</v>
       </c>
       <c r="G2">
         <v>266.666675987241</v>
@@ -8547,7 +8547,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -8559,16 +8559,16 @@
         <v>15.04993697229343</v>
       </c>
       <c r="N2">
-        <v>0.5773502691952341</v>
+        <v>0.577350269195234</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.5773502691743765</v>
+        <v>0.5773502691743764</v>
       </c>
       <c r="Q2">
-        <v>-5.812885219395885E-09</v>
+        <v>-5.812891580505249E-09</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -8577,7 +8577,7 @@
         <v>179.9999999936331</v>
       </c>
       <c r="T2">
-        <v>4.198911195821409</v>
+        <v>4.19891119582141</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -8621,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.5773502690917837</v>
+        <v>0.5773502690917839</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.5773502692819935</v>
+        <v>0.5773502692819937</v>
       </c>
       <c r="Q3">
-        <v>5.928719920660776E-10</v>
+        <v>5.928523598746902E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>179.9999999993227</v>
+        <v>179.9999999993228</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8683,16 +8683,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.5773502690912237</v>
+        <v>0.577350269091224</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.5773502693301086</v>
+        <v>0.577350269330109</v>
       </c>
       <c r="Q4">
-        <v>6.074372594463963E-09</v>
+        <v>6.074352101551187E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -8745,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.3333333328411343</v>
+        <v>0.5773502689262676</v>
       </c>
       <c r="O5">
-        <v>0.3333333338615928</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.6666666667027271</v>
+        <v>0.577350269515388</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999692109</v>
+        <v>1.785448388499469E-08</v>
       </c>
       <c r="R5">
-        <v>179.9999999919939</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.139147616625086E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.3333333328411341</v>
+        <v>0.5773502689262676</v>
       </c>
       <c r="O6">
-        <v>0.3333333338615929</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6666666667027271</v>
+        <v>0.5773502695153883</v>
       </c>
       <c r="Q6">
-        <v>-179.999999969211</v>
+        <v>1.785447762822763E-08</v>
       </c>
       <c r="R6">
-        <v>179.9999999919939</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.139147065736856E-08</v>
+        <v>-179.9999999950684</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8911,7 +8911,7 @@
         <v>3.012913138951925</v>
       </c>
       <c r="D2">
-        <v>3.012913138593917</v>
+        <v>3.012913138593919</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -8929,7 +8929,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -8953,13 +8953,13 @@
         <v>8.109158318802283</v>
       </c>
       <c r="R2">
-        <v>-117.0248837767961</v>
+        <v>-117.0248837767962</v>
       </c>
       <c r="S2">
         <v>161.7746336318227</v>
       </c>
       <c r="T2">
-        <v>3.012913138737344</v>
+        <v>3.012913138737345</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -9003,19 +9003,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7472997526418613</v>
+        <v>0.7472997526418615</v>
       </c>
       <c r="O3">
         <v>0.3354590830770561</v>
       </c>
       <c r="P3">
-        <v>0.6184267550841063</v>
+        <v>0.6184267550841064</v>
       </c>
       <c r="Q3">
-        <v>8.109158321931385</v>
+        <v>8.109158321931375</v>
       </c>
       <c r="R3">
-        <v>-117.0248837562164</v>
+        <v>-117.0248837562165</v>
       </c>
       <c r="S3">
         <v>161.7746336387373</v>
@@ -9065,19 +9065,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7472997526385887</v>
+        <v>0.7472997526385891</v>
       </c>
       <c r="O4">
-        <v>0.3354590831006823</v>
+        <v>0.3354590831006825</v>
       </c>
       <c r="P4">
-        <v>0.6184267551237352</v>
+        <v>0.6184267551237355</v>
       </c>
       <c r="Q4">
-        <v>8.109158324959907</v>
+        <v>8.109158324959896</v>
       </c>
       <c r="R4">
-        <v>-117.0248837452071</v>
+        <v>-117.0248837452072</v>
       </c>
       <c r="S4">
         <v>161.7746336388059</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5655462790792672</v>
+        <v>0.7472997525143643</v>
       </c>
       <c r="O5">
-        <v>0.3792589158205199</v>
+        <v>0.3354590829610918</v>
       </c>
       <c r="P5">
-        <v>0.7679592756105803</v>
+        <v>0.6184267552078961</v>
       </c>
       <c r="Q5">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815616</v>
       </c>
       <c r="R5">
-        <v>131.4656840457361</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S5">
-        <v>-3.793471518191353</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9189,22 +9189,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.565546279079267</v>
+        <v>0.7472997525143643</v>
       </c>
       <c r="O6">
-        <v>0.3792589158205199</v>
+        <v>0.3354590829610916</v>
       </c>
       <c r="P6">
-        <v>0.7679592756105803</v>
+        <v>0.6184267552078961</v>
       </c>
       <c r="Q6">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815612</v>
       </c>
       <c r="R6">
-        <v>131.4656840457361</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S6">
-        <v>-3.793471518191365</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9293,7 +9293,7 @@
         <v>3.012913138951925</v>
       </c>
       <c r="D2">
-        <v>3.012913138593917</v>
+        <v>3.012913138593919</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -9311,7 +9311,7 @@
         <v>15.04993697142863</v>
       </c>
       <c r="J2">
-        <v>1.504993721671082</v>
+        <v>1.504993721671081</v>
       </c>
       <c r="K2">
         <v>15.04993697236766</v>
@@ -9335,13 +9335,13 @@
         <v>8.109158318802283</v>
       </c>
       <c r="R2">
-        <v>-117.0248837767961</v>
+        <v>-117.0248837767962</v>
       </c>
       <c r="S2">
         <v>161.7746336318227</v>
       </c>
       <c r="T2">
-        <v>3.012913138737344</v>
+        <v>3.012913138737345</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -9385,19 +9385,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7472997526418613</v>
+        <v>0.7472997526418615</v>
       </c>
       <c r="O3">
         <v>0.3354590830770561</v>
       </c>
       <c r="P3">
-        <v>0.6184267550841063</v>
+        <v>0.6184267550841064</v>
       </c>
       <c r="Q3">
-        <v>8.109158321931385</v>
+        <v>8.109158321931375</v>
       </c>
       <c r="R3">
-        <v>-117.0248837562164</v>
+        <v>-117.0248837562165</v>
       </c>
       <c r="S3">
         <v>161.7746336387373</v>
@@ -9447,19 +9447,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7472997526385887</v>
+        <v>0.7472997526385891</v>
       </c>
       <c r="O4">
-        <v>0.3354590831006823</v>
+        <v>0.3354590831006825</v>
       </c>
       <c r="P4">
-        <v>0.6184267551237352</v>
+        <v>0.6184267551237355</v>
       </c>
       <c r="Q4">
-        <v>8.109158324959907</v>
+        <v>8.109158324959896</v>
       </c>
       <c r="R4">
-        <v>-117.0248837452071</v>
+        <v>-117.0248837452072</v>
       </c>
       <c r="S4">
         <v>161.7746336388059</v>
@@ -9509,22 +9509,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5655462790792672</v>
+        <v>0.7472997525143643</v>
       </c>
       <c r="O5">
-        <v>0.3792589158205199</v>
+        <v>0.3354590829610918</v>
       </c>
       <c r="P5">
-        <v>0.7679592756105803</v>
+        <v>0.6184267552078961</v>
       </c>
       <c r="Q5">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815616</v>
       </c>
       <c r="R5">
-        <v>131.4656840457361</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S5">
-        <v>-3.793471518191353</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.565546279079267</v>
+        <v>0.7472997525143643</v>
       </c>
       <c r="O6">
-        <v>0.3792589158205199</v>
+        <v>0.3354590829610916</v>
       </c>
       <c r="P6">
-        <v>0.7679592756105803</v>
+        <v>0.6184267552078961</v>
       </c>
       <c r="Q6">
-        <v>-155.6266319927826</v>
+        <v>8.109158330815612</v>
       </c>
       <c r="R6">
-        <v>131.4656840457361</v>
+        <v>-117.0248837092546</v>
       </c>
       <c r="S6">
-        <v>-3.793471518191365</v>
+        <v>161.7746336498391</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9630,22 +9630,22 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>3.617960382498488</v>
+        <v>3.617960382498489</v>
       </c>
       <c r="C2">
-        <v>689.314032248458</v>
+        <v>689.3140322484581</v>
       </c>
       <c r="D2">
-        <v>1.324394473835048</v>
+        <v>1.324394473835047</v>
       </c>
       <c r="E2">
         <v>13.24394453564036</v>
       </c>
       <c r="F2">
-        <v>0.4028253111823096</v>
+        <v>0.4028253111823098</v>
       </c>
       <c r="G2">
-        <v>45.00000000004623</v>
+        <v>45.00000000004626</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9665,10 +9665,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.4028253110876379</v>
+        <v>0.4028253110876387</v>
       </c>
       <c r="G3">
-        <v>-25.88075857997293</v>
+        <v>-25.88075857997276</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9688,10 +9688,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.4028253110894423</v>
+        <v>0.4028253110894434</v>
       </c>
       <c r="G4">
-        <v>-25.8807585729802</v>
+        <v>-25.88075857298002</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.4028253109423526</v>
+        <v>0.4028253109423234</v>
       </c>
       <c r="G5">
-        <v>-175.8807585414167</v>
+        <v>-25.88075854142508</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.4028253109423526</v>
+        <v>0.4028253109423234</v>
       </c>
       <c r="G6">
-        <v>-175.8807585414167</v>
+        <v>-25.88075854142508</v>
       </c>
     </row>
   </sheetData>
@@ -9778,13 +9778,13 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>4.198911195753388</v>
+        <v>4.198911195753389</v>
       </c>
       <c r="C2">
-        <v>800.0000280266122</v>
+        <v>800.0000280266123</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -9926,13 +9926,13 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>4.198911195753388</v>
+        <v>4.198911195753389</v>
       </c>
       <c r="C2">
-        <v>800.0000280266122</v>
+        <v>800.0000280266123</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -10080,7 +10080,7 @@
         <v>574.0370498678898</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -10089,7 +10089,7 @@
         <v>0.3354590831385725</v>
       </c>
       <c r="G2">
-        <v>44.99999999355204</v>
+        <v>44.99999999355207</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10109,10 +10109,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3354590830466709</v>
+        <v>0.3354590830466711</v>
       </c>
       <c r="G3">
-        <v>-27.02488376071828</v>
+        <v>-27.02488376071815</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10132,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.3354590830702971</v>
+        <v>0.3354590830702975</v>
       </c>
       <c r="G4">
-        <v>-27.02488374970901</v>
+        <v>-27.02488374970884</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10155,10 +10155,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.3354590829307355</v>
+        <v>0.3354590829307066</v>
       </c>
       <c r="G5">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375628</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3354590829307355</v>
+        <v>0.3354590829307066</v>
       </c>
       <c r="G6">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375628</v>
       </c>
     </row>
   </sheetData>
@@ -10228,7 +10228,7 @@
         <v>574.0370498678898</v>
       </c>
       <c r="D2">
-        <v>1.504993721305345</v>
+        <v>1.504993721305343</v>
       </c>
       <c r="E2">
         <v>15.04993697229389</v>
@@ -10237,7 +10237,7 @@
         <v>0.3354590831385725</v>
       </c>
       <c r="G2">
-        <v>44.99999999355204</v>
+        <v>44.99999999355207</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10257,10 +10257,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.3354590830466709</v>
+        <v>0.3354590830466711</v>
       </c>
       <c r="G3">
-        <v>-27.02488376071828</v>
+        <v>-27.02488376071815</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10280,10 +10280,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.3354590830702971</v>
+        <v>0.3354590830702975</v>
       </c>
       <c r="G4">
-        <v>-27.02488374970901</v>
+        <v>-27.02488374970884</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10303,10 +10303,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.3354590829307355</v>
+        <v>0.3354590829307066</v>
       </c>
       <c r="G5">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375628</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10326,10 +10326,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.3354590829307355</v>
+        <v>0.3354590829307066</v>
       </c>
       <c r="G6">
-        <v>-177.0248837137474</v>
+        <v>-27.02488371375628</v>
       </c>
     </row>
   </sheetData>
@@ -10430,7 +10430,7 @@
         <v>13.24394453497027</v>
       </c>
       <c r="J2">
-        <v>1.324394473632983</v>
+        <v>1.324394473632982</v>
       </c>
       <c r="K2">
         <v>13.24394453600777</v>
@@ -10448,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.9526279647833884</v>
+        <v>0.9526279647833883</v>
       </c>
       <c r="Q2">
-        <v>-8.694415824817534E-11</v>
+        <v>-8.694545057164095E-11</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -10501,16 +10501,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9526279646671958</v>
+        <v>0.9526279646671957</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.9526279648965611</v>
+        <v>0.9526279648965608</v>
       </c>
       <c r="Q3">
-        <v>1.457313170724292E-10</v>
+        <v>1.457223144658843E-10</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -10560,16 +10560,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9526279646404247</v>
+        <v>0.9526279646404244</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.9526279649233325</v>
+        <v>0.952627964923332</v>
       </c>
       <c r="Q4">
-        <v>1.564857035622748E-09</v>
+        <v>1.564840543881781E-09</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.5500000113416785</v>
+        <v>0.9526279644570351</v>
       </c>
       <c r="O5">
-        <v>0.5500000124670777</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.100000023808756</v>
+        <v>0.9526279651067214</v>
       </c>
       <c r="Q5">
-        <v>-179.9999999919767</v>
+        <v>2.673396028003744E-09</v>
       </c>
       <c r="R5">
-        <v>179.9999999919778</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5.542269350069056E-13</v>
+        <v>179.9999999973179</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -10678,22 +10678,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.5500000113416785</v>
+        <v>0.9526279644570351</v>
       </c>
       <c r="O6">
-        <v>0.5500000124670777</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.100000023808756</v>
+        <v>0.9526279651067214</v>
       </c>
       <c r="Q6">
-        <v>-179.9999999919767</v>
+        <v>2.673397441865751E-09</v>
       </c>
       <c r="R6">
-        <v>179.9999999919778</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>5.341946361512343E-13</v>
+        <v>179.9999999973179</v>
       </c>
     </row>
   </sheetData>
